--- a/data_out/country_spreadsheets/North Macedonia.xlsx
+++ b/data_out/country_spreadsheets/North Macedonia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>149.49</v>
       </c>
+      <c r="X2" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>194.7</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>112.59</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>81.17</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>289.09</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>69.78</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>283.41</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>167.06</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>142.44</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>121.73</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>267.78</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>149.49</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>134.91</v>
       </c>
+      <c r="X3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>123.45</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>274.8</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>273.96</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>198.17</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>88.93000000000001</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>86.68000000000001</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>172.65</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>134.91</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>184.52</v>
       </c>
+      <c r="X4" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>191.33</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>25.17</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>190.85</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>78.92</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>189.58</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>85.16</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>111.36</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>98.70999999999999</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>100.32</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>184.52</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>124.75</v>
       </c>
+      <c r="X5" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>229.15</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>75.97</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>251.8</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>135.58</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>127.78</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>229.32</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>124.75</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>227.58</v>
       </c>
+      <c r="X6" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>176.3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>123.69</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>62.42</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>306.41</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>96.27</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>255.22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>211.97</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>97.72</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>193.78</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>284.55</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>227.58</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>167.81</v>
       </c>
+      <c r="X7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>189.02</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>69.95999999999999</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>119.27</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>84.34999999999999</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>154.81</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>167.81</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>121.15</v>
       </c>
+      <c r="X8" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>64.78</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>231.74</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>124.45</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>106.03</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>215.52</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>71.15000000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>259.4</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>69.01000000000001</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>121.15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1158,6 +1600,57 @@
         <v>187.81</v>
       </c>
       <c r="W9" t="n">
+        <v>183.49</v>
+      </c>
+      <c r="X9" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>92.76000000000001</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>273.46</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>300.32</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>109.73</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>67.83</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>275.91</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>202.88</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>130.28</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>53.27</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>105.18</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>187.81</v>
+      </c>
+      <c r="AN9" t="n">
         <v>183.49</v>
       </c>
     </row>
